--- a/Excel practice.xlsx
+++ b/Excel practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF094D3-9B23-40BE-9BE7-0DDEDB8E1E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D8361-F604-4DC1-9972-C937DAB616C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="formulasbasic" sheetId="2" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="190">
   <si>
     <t>Date</t>
   </si>
@@ -570,6 +570,87 @@
   </si>
   <si>
     <t>avgifs</t>
+  </si>
+  <si>
+    <t>Basic Formulas</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>round</t>
+  </si>
+  <si>
+    <t>Date Functions</t>
+  </si>
+  <si>
+    <t>Date()</t>
+  </si>
+  <si>
+    <t>NERWORDAYS()</t>
+  </si>
+  <si>
+    <t>YEAR()</t>
+  </si>
+  <si>
+    <t>MONTH()</t>
+  </si>
+  <si>
+    <t>DAY()</t>
+  </si>
+  <si>
+    <t>WEEKDAY()</t>
+  </si>
+  <si>
+    <t>EOMONTH()</t>
+  </si>
+  <si>
+    <t>String Funcitons</t>
+  </si>
+  <si>
+    <t>Find</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>Sustitute</t>
+  </si>
+  <si>
+    <t>Concat</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>math functions</t>
+  </si>
+  <si>
+    <t>SQRT</t>
+  </si>
+  <si>
+    <t>Fact</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>Roundup</t>
+  </si>
+  <si>
+    <t>Rounddown</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
@@ -16051,6 +16132,8 @@
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16080,7 +16163,6 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -16241,6 +16323,12 @@
       <c r="F9">
         <v>18</v>
       </c>
+      <c r="L9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -16261,6 +16349,18 @@
       <c r="F10">
         <v>8</v>
       </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -16281,6 +16381,18 @@
       <c r="F11">
         <v>18</v>
       </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
@@ -16301,6 +16413,18 @@
       <c r="F12">
         <v>13</v>
       </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
@@ -16321,6 +16445,18 @@
       <c r="F13">
         <v>13</v>
       </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>164</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -16341,6 +16477,18 @@
       <c r="F14">
         <v>13</v>
       </c>
+      <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>165</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -16361,6 +16509,18 @@
       <c r="F15">
         <v>9</v>
       </c>
+      <c r="K15">
+        <v>6</v>
+      </c>
+      <c r="L15" t="s">
+        <v>166</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -16381,8 +16541,14 @@
       <c r="F16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <v>7</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>14</v>
       </c>
@@ -16401,8 +16567,14 @@
       <c r="F17">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
@@ -16421,8 +16593,14 @@
       <c r="F18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K18">
+        <v>9</v>
+      </c>
+      <c r="L18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>21</v>
       </c>
@@ -16441,8 +16619,14 @@
       <c r="F19">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
@@ -16461,8 +16645,14 @@
       <c r="F20">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K20">
+        <v>11</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
@@ -16482,7 +16672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>24</v>
       </c>
@@ -16501,8 +16691,14 @@
       <c r="F22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>25</v>
       </c>
@@ -16521,8 +16717,20 @@
       <c r="F23">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>169</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>26</v>
       </c>
@@ -16541,8 +16749,20 @@
       <c r="F24">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24" t="s">
+        <v>122</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
@@ -16561,8 +16781,20 @@
       <c r="F25">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K25">
+        <v>3</v>
+      </c>
+      <c r="L25" t="s">
+        <v>170</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -16581,8 +16813,20 @@
       <c r="F26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26" t="s">
+        <v>171</v>
+      </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
+      <c r="O26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>29</v>
       </c>
@@ -16601,8 +16845,20 @@
       <c r="F27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K27">
+        <v>5</v>
+      </c>
+      <c r="L27" t="s">
+        <v>172</v>
+      </c>
+      <c r="N27">
+        <v>5</v>
+      </c>
+      <c r="O27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>10</v>
       </c>
@@ -16621,8 +16877,20 @@
       <c r="F28">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K28">
+        <v>6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>173</v>
+      </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
+      <c r="O28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
@@ -16641,8 +16909,20 @@
       <c r="F29">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K29">
+        <v>7</v>
+      </c>
+      <c r="L29" t="s">
+        <v>174</v>
+      </c>
+      <c r="N29">
+        <v>7</v>
+      </c>
+      <c r="O29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
@@ -16661,8 +16941,20 @@
       <c r="F30">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="K30">
+        <v>8</v>
+      </c>
+      <c r="L30" t="s">
+        <v>175</v>
+      </c>
+      <c r="N30">
+        <v>8</v>
+      </c>
+      <c r="O30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>32</v>
       </c>
@@ -16681,8 +16973,14 @@
       <c r="F31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N31">
+        <v>9</v>
+      </c>
+      <c r="O31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>33</v>
       </c>
@@ -16701,8 +16999,14 @@
       <c r="F32">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N32">
+        <v>10</v>
+      </c>
+      <c r="O32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>34</v>
       </c>
@@ -16721,8 +17025,14 @@
       <c r="F33">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N33">
+        <v>11</v>
+      </c>
+      <c r="O33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>35</v>
       </c>
@@ -16741,8 +17051,14 @@
       <c r="F34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N34">
+        <v>12</v>
+      </c>
+      <c r="O34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>36</v>
       </c>
@@ -16762,7 +17078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
@@ -16782,7 +17098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>16</v>
       </c>
@@ -16802,7 +17118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>38</v>
       </c>
@@ -16822,7 +17138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>6</v>
       </c>
@@ -16842,7 +17158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>31</v>
       </c>
@@ -16862,7 +17178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
@@ -16882,7 +17198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>40</v>
       </c>
@@ -16902,7 +17218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>38</v>
       </c>
@@ -16922,7 +17238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>41</v>
       </c>
@@ -16942,7 +17258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>42</v>
       </c>
@@ -16962,7 +17278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>43</v>
       </c>
@@ -16982,7 +17298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>44</v>
       </c>
@@ -17002,7 +17318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>45</v>
       </c>
